--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6164-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6164-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D6CC545-1C5B-4FB2-8A8D-92DE942002C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37E8FF9C-BA24-4138-8211-64BCF956716B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{8CCFA45D-3E5F-4E52-9669-3E5B7501694B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CC61BDE3-3B00-4E31-8F15-0F0799189E23}"/>
   </bookViews>
   <sheets>
     <sheet name="6164-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1439,23 +1439,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F41ADC-0C00-4072-A45A-56148D334FA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8780BCE7-9B22-4838-BF0E-ECE5B6ABE8A9}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +1482,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1513,7 +1512,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1609,7 +1608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1663,7 +1662,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1717,7 +1716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1771,7 +1770,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1825,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1879,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2020</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>26</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2019</v>
       </c>
@@ -2043,7 +2042,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2211,7 +2210,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2018</v>
       </c>
@@ -2265,7 +2264,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2017</v>
       </c>
@@ -2319,7 +2318,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2016</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2015</v>
       </c>
@@ -2427,7 +2426,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2014</v>
       </c>
@@ -2481,7 +2480,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2013</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2012</v>
       </c>
@@ -2589,7 +2588,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2011</v>
       </c>
@@ -2643,7 +2642,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2010</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2009</v>
       </c>
@@ -2751,7 +2750,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2008</v>
       </c>
@@ -2805,7 +2804,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2007</v>
       </c>
@@ -2859,7 +2858,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2006</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2005</v>
       </c>
@@ -2967,7 +2966,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2004</v>
       </c>
@@ -3021,7 +3020,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2003</v>
       </c>
@@ -3075,7 +3074,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2002</v>
       </c>
@@ -3129,7 +3128,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2001</v>
       </c>
@@ -3183,7 +3182,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2000</v>
       </c>
@@ -3237,7 +3236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>1999</v>
       </c>
@@ -3291,7 +3290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39" t="s">
         <v>32</v>
       </c>
